--- a/outputs/evaluation/requirement/design/v2/gemini-3-5-flash-lite/CF_M05/first/CF_M05_req_eval.xlsx
+++ b/outputs/evaluation/requirement/design/v2/gemini-3-5-flash-lite/CF_M05/first/CF_M05_req_eval.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -546,6 +551,9 @@
         <v>0.9615</v>
       </c>
       <c r="D13" t="n">
+        <v>0.6579</v>
+      </c>
+      <c r="E13" t="n">
         <v>0.8847</v>
       </c>
     </row>
@@ -755,14 +763,11 @@
           <t>Cap usuari pot accedir a dades d’altres clients.</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>R_49</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -776,14 +781,11 @@
           <t>No user can access data from other customers.</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>CF_M05_R24</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -819,9 +821,6 @@
           <t>C_04</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>QR</t>
@@ -845,8 +844,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -877,14 +874,11 @@
           <t>Traduccions completes i correctes en ambdues llengües.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>R_37</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -898,14 +892,11 @@
           <t>Complete and correct translations in both languages.</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>CF_M05_R12</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -936,10 +927,6 @@
           <t>Donar o treure accés a aplicacions als usuaris.</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>FR</t>
@@ -953,10 +940,6 @@
           <t>Give or remove access to applications from users.</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -987,14 +970,11 @@
           <t>La disponibilitat del sistema ha de ser de mínim 99,9%, fins i tot durant els moments d’ús intensiu.</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>R_45</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1009,14 +989,11 @@
 during times of intensive use.</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>CF_M05_R20</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1047,14 +1024,11 @@
           <t>La disponibilitat del sistema ha de ser de mínim 99,9%, fins i tot durant els moments d’ús intensiu.</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>R_43</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1068,14 +1042,11 @@
           <t>System availability must be at least 99.9%, even during times of intensive use.</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>CF_M05_R18</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1106,10 +1077,6 @@
           <t>Convertir qualsevol menció de l’antic nom al nou nom.</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1123,10 +1090,6 @@
           <t>Convert any mention of the old name to the new name.</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1162,9 +1125,6 @@
           <t>C_05</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1188,8 +1148,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1220,14 +1178,11 @@
           <t>Temps de resposta no ha superar 1 segon en el 95% de les consultes.</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>R_41</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1241,14 +1196,11 @@
           <t>Response time should not exceed 1 second in 95% of queries.</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>CF_M05_R16</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1279,14 +1231,11 @@
           <t>El temps d’aprenentatge per les noves funcionalitats no hauria de superar els 5 min.</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>R_39</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1300,14 +1249,11 @@
           <t>Learning time for new features should not exceed 5 min.</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>CF_M05_R14</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1343,9 +1289,6 @@
           <t>C_07</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1370,8 +1313,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1402,10 +1343,6 @@
           <t>Accedir al portal mitjançant una autentificació de credencials personals.</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1419,10 +1356,6 @@
           <t>Access the portal using credential authentication personal.</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1458,9 +1391,6 @@
           <t>C_03</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1484,8 +1414,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1516,10 +1444,6 @@
           <t>Restringir la visualització i les accions (crear, modificar i eliminar) sobre dades segons els rols assignats a l’usuari.</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1533,10 +1457,6 @@
           <t>Restrict actions (create, modify and delete) on data according to the roles assigned to the user.</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1567,10 +1487,6 @@
           <t>Garantir que no es pot accedir a les dades d’altres clients.</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1584,10 +1500,6 @@
           <t>Ensure that other customers' data cannot be accessed.</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1618,14 +1530,11 @@
           <t>El sistema ha de disposar d’un mecanisme segur d’autenticació i verificació de permisos per assegurar que cada usuari només pugui accedir a la informació i funcionalitats que li corresponen.</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>R_47</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1639,14 +1548,11 @@
           <t>The system must have a secure authentication mechanism and permission verification to ensure that each user can only access the information and functionalities that correspond to it.</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>CF_M05_R22</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1677,14 +1583,11 @@
           <t>El 80% dels usuaris no necessiten demanar a ajuda a tercer per a fer servir l’aplicació.</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>R_35</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1699,14 +1602,11 @@
 use the application.</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>CF_M05_R10</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1742,9 +1642,6 @@
           <t>C_08</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1769,8 +1666,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1801,14 +1696,11 @@
           <t>El disseny, colors, tipografies i organització han de ser consistents amb l’antiga versió.</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>R_33</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1822,14 +1714,11 @@
           <t>The design, organization, colors and typoghraphy must be consistent with the old version.</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>CF_M05_R08</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1865,9 +1754,6 @@
           <t>C_09</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1891,8 +1777,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1928,9 +1812,6 @@
           <t>C_02</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1954,8 +1835,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1991,9 +1870,6 @@
           <t>C_01</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>QR</t>
@@ -2017,8 +1893,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2049,10 +1923,6 @@
           <t>Accedir a les aplicacions a les quals té accés en el portal.</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>FR</t>
@@ -2066,10 +1936,6 @@
           <t>Access the applications to which the user has access on the portal.</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2105,9 +1971,6 @@
           <t>C_06</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>QR</t>
@@ -2132,8 +1995,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2164,10 +2025,6 @@
           <t>Visualitzar les aplicacions del portal a les quals l’usuari té accés.</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>FR</t>
@@ -2181,10 +2038,6 @@
           <t>View the portal applications to which the user has access.</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
